--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.40316068832807</v>
+        <v>3.153013611853312</v>
       </c>
       <c r="D2" t="n">
-        <v>19.35630251508196</v>
+        <v>3.145399158700819</v>
       </c>
       <c r="E2" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F2" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.57499727346583</v>
+        <v>3.180937056938198</v>
       </c>
       <c r="D3" t="n">
-        <v>19.49360972048945</v>
+        <v>3.167711579579536</v>
       </c>
       <c r="E3" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F3" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.63212281236144</v>
+        <v>3.677719957008734</v>
       </c>
       <c r="D4" t="n">
-        <v>23.19768223278719</v>
+        <v>3.769623362827918</v>
       </c>
       <c r="E4" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F4" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.41830728099836</v>
+        <v>3.480474933162233</v>
       </c>
       <c r="D5" t="n">
-        <v>21.19072849310831</v>
+        <v>3.4434933801301</v>
       </c>
       <c r="E5" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F5" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.26245330691869</v>
+        <v>2.642648662374287</v>
       </c>
       <c r="D6" t="n">
-        <v>15.52748629527992</v>
+        <v>2.523216522982988</v>
       </c>
       <c r="E6" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F6" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.41441864224711</v>
+        <v>3.642343029365155</v>
       </c>
       <c r="D7" t="n">
-        <v>21.4897386534949</v>
+        <v>3.492082531192921</v>
       </c>
       <c r="E7" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F7" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.88023851338112</v>
+        <v>2.580538758424431</v>
       </c>
       <c r="D8" t="n">
-        <v>16.183016923026</v>
+        <v>2.629740249991726</v>
       </c>
       <c r="E8" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F8" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.02038786716826</v>
+        <v>2.765813028414843</v>
       </c>
       <c r="D9" t="n">
-        <v>16.37937654872385</v>
+        <v>2.661648689167627</v>
       </c>
       <c r="E9" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F9" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.75845274259482</v>
+        <v>2.398248570671659</v>
       </c>
       <c r="D10" t="n">
-        <v>14.71582653397997</v>
+        <v>2.391321811771746</v>
       </c>
       <c r="E10" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F10" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.19086678513361</v>
+        <v>3.768515852584212</v>
       </c>
       <c r="D11" t="n">
-        <v>23.17422868163345</v>
+        <v>3.765812160765436</v>
       </c>
       <c r="E11" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F11" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.20905339633483</v>
+        <v>3.608971176904411</v>
       </c>
       <c r="D12" t="n">
-        <v>21.70959933756522</v>
+        <v>3.527809892354349</v>
       </c>
       <c r="E12" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F12" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.37136589996869</v>
+        <v>5.747846958744913</v>
       </c>
       <c r="D13" t="n">
-        <v>34.74980759141029</v>
+        <v>5.646843733604172</v>
       </c>
       <c r="E13" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F13" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.59691470212304</v>
+        <v>7.084498639094994</v>
       </c>
       <c r="D14" t="n">
-        <v>42.95449925887475</v>
+        <v>6.980106129567148</v>
       </c>
       <c r="E14" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F14" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.81685924921759</v>
+        <v>7.607739627997858</v>
       </c>
       <c r="D15" t="n">
-        <v>46.85895082641684</v>
+        <v>7.614579509292738</v>
       </c>
       <c r="E15" t="n">
-        <v>9.812612154375088</v>
+        <v>1.594549475085952</v>
       </c>
       <c r="F15" t="n">
-        <v>9.77273633176836</v>
+        <v>1.588069653912359</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
